--- a/Custom field options_2026.xlsx
+++ b/Custom field options_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\MI2PEPF00000297\EXCELCNV\d7d66922-1ff7-49b5-af65-0b42c24bbb81\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\University of Bern\Wyss Academy\Dashboard_Emissions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80F44F8A-5689-41B3-916B-897634999921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF3D11C-5F05-43D9-81F9-5C2E52220C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{1F1D891C-1E42-41CB-9B32-CA07EEE52EB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1F1D891C-1E42-41CB-9B32-CA07EEE52EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="215">
   <si>
     <t>Name</t>
   </si>
@@ -47,15 +47,9 @@
     <t>1.1.1</t>
   </si>
   <si>
-    <t>Co-design, knowledge and engagement, monitoring</t>
-  </si>
-  <si>
     <t>1.1.2</t>
   </si>
   <si>
-    <t>Increased habitat connectivity</t>
-  </si>
-  <si>
     <t>1.1.3</t>
   </si>
   <si>
@@ -71,24 +65,9 @@
     <t>1.1.5</t>
   </si>
   <si>
-    <t>Improved rangeland quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2.2 </t>
-  </si>
-  <si>
-    <t>Integrated wetland management for increased biomass production &amp; water</t>
-  </si>
-  <si>
     <t>1.2.3</t>
   </si>
   <si>
-    <t>Ecosystem connectivity for improved wildlife movements and reduced human wildlife conflicts</t>
-  </si>
-  <si>
     <t>1.2.4</t>
   </si>
   <si>
@@ -119,9 +98,6 @@
     <t>1.3.4</t>
   </si>
   <si>
-    <t>Alternative livelihoods for households with limited access to land</t>
-  </si>
-  <si>
     <t>1.3.5</t>
   </si>
   <si>
@@ -131,33 +107,15 @@
     <t>1.4.1</t>
   </si>
   <si>
-    <t>Co-desing, knowledge and engagement, monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4.2 </t>
-  </si>
-  <si>
-    <t>Inclusive territorial governance and policy implementation</t>
-  </si>
-  <si>
     <t>1.4.3</t>
   </si>
   <si>
-    <t>Scaling transformative innovation for resilient livelihoods</t>
-  </si>
-  <si>
     <t>1.4.4</t>
   </si>
   <si>
-    <t>Forest conservation through nature-based livelihoods</t>
-  </si>
-  <si>
     <t>1.4.5</t>
   </si>
   <si>
-    <t>Productive restoration of degraded landscapes</t>
-  </si>
-  <si>
     <t>1.5.1</t>
   </si>
   <si>
@@ -182,15 +140,9 @@
     <t>1.6.1</t>
   </si>
   <si>
-    <t>Climate-smart regions</t>
-  </si>
-  <si>
     <t>1.6.2</t>
   </si>
   <si>
-    <t>Thriving lands, flourishing future for nature and people</t>
-  </si>
-  <si>
     <t>2.1.1</t>
   </si>
   <si>
@@ -218,9 +170,6 @@
     <t>2.3.1</t>
   </si>
   <si>
-    <t>Engaging with other effective area-based conservation measures</t>
-  </si>
-  <si>
     <t>2.3.2</t>
   </si>
   <si>
@@ -230,9 +179,6 @@
     <t>3.1.1</t>
   </si>
   <si>
-    <t>Adaptive culture and organization</t>
-  </si>
-  <si>
     <t>3.1.2</t>
   </si>
   <si>
@@ -260,14 +206,488 @@
     <t>3.3.2</t>
   </si>
   <si>
-    <t>Monitoring, Evaluation and Learning</t>
+    <t>BRN1000</t>
+  </si>
+  <si>
+    <t>HQ Institutional</t>
+  </si>
+  <si>
+    <t>BRN1100</t>
+  </si>
+  <si>
+    <t>HQ CEO</t>
+  </si>
+  <si>
+    <t>BRN1200</t>
+  </si>
+  <si>
+    <t>HQ COO</t>
+  </si>
+  <si>
+    <t>BRN4300</t>
+  </si>
+  <si>
+    <t>HQ COM</t>
+  </si>
+  <si>
+    <t>SAM1000</t>
+  </si>
+  <si>
+    <t>SAM Management &amp; Support</t>
+  </si>
+  <si>
+    <t>EAF1000</t>
+  </si>
+  <si>
+    <t>EAF Management &amp; Support</t>
+  </si>
+  <si>
+    <t>SEA1000</t>
+  </si>
+  <si>
+    <t>SEA Management &amp; Support</t>
+  </si>
+  <si>
+    <t>BRN2000</t>
+  </si>
+  <si>
+    <t>HQ Operations / Resources</t>
+  </si>
+  <si>
+    <t>BRN2100</t>
+  </si>
+  <si>
+    <t>HQ FIN</t>
+  </si>
+  <si>
+    <t>BRN2200</t>
+  </si>
+  <si>
+    <t>HQ HRM</t>
+  </si>
+  <si>
+    <t>BRN2300</t>
+  </si>
+  <si>
+    <t>HQ ICT</t>
+  </si>
+  <si>
+    <t>BRN2400</t>
+  </si>
+  <si>
+    <t>HQ LOG</t>
+  </si>
+  <si>
+    <t>BRN3000</t>
+  </si>
+  <si>
+    <t>HQ Research</t>
+  </si>
+  <si>
+    <t>BRN3100</t>
+  </si>
+  <si>
+    <t>HQ Climate Change</t>
+  </si>
+  <si>
+    <t>BRN3200</t>
+  </si>
+  <si>
+    <t>HQ Biodiversity</t>
+  </si>
+  <si>
+    <t>BRN3300</t>
+  </si>
+  <si>
+    <t>HQ Land Systems</t>
+  </si>
+  <si>
+    <t>BRN3400</t>
+  </si>
+  <si>
+    <t>HQ Governance Innovation</t>
+  </si>
+  <si>
+    <t>BRN3500</t>
+  </si>
+  <si>
+    <t>HQ Political Economy</t>
+  </si>
+  <si>
+    <t>BRN4500</t>
+  </si>
+  <si>
+    <t>HQ ICT for Nature</t>
+  </si>
+  <si>
+    <t>BRN4100</t>
+  </si>
+  <si>
+    <t>HQ Policy Outreach</t>
+  </si>
+  <si>
+    <t>BRN3700</t>
+  </si>
+  <si>
+    <t>HQ Synthesis Center</t>
+  </si>
+  <si>
+    <t>BRN5000</t>
+  </si>
+  <si>
+    <t>HQ Regional stewardship hubs</t>
+  </si>
+  <si>
+    <t>BRN6000</t>
+  </si>
+  <si>
+    <t>CH Bern Hub</t>
+  </si>
+  <si>
+    <t>LIM5000</t>
+  </si>
+  <si>
+    <t>Operations Peru (Incubator)</t>
+  </si>
+  <si>
+    <t>NYK5000</t>
+  </si>
+  <si>
+    <t>Operations Kenya (Incubator)</t>
+  </si>
+  <si>
+    <t>VTE5000</t>
+  </si>
+  <si>
+    <t>Operations Laos (Incubator)</t>
+  </si>
+  <si>
+    <t>BRN2500</t>
+  </si>
+  <si>
+    <t>HQ Mel</t>
+  </si>
+  <si>
+    <t>BRN9000</t>
+  </si>
+  <si>
+    <t>HQ Time Difference</t>
+  </si>
+  <si>
+    <t>HQ Income</t>
+  </si>
+  <si>
+    <t>TNR5000</t>
+  </si>
+  <si>
+    <t>Operations Madagascar (Incubator)</t>
+  </si>
+  <si>
+    <t>BKK5000</t>
+  </si>
+  <si>
+    <t>Operations Thailand (Incubator)</t>
+  </si>
+  <si>
+    <t>BRN4000</t>
+  </si>
+  <si>
+    <t>HQ Engagement Center</t>
+  </si>
+  <si>
+    <t>BRN2600</t>
+  </si>
+  <si>
+    <t>HQ Funding &amp; Acquisition</t>
+  </si>
+  <si>
+    <t>BRN4400</t>
+  </si>
+  <si>
+    <t>HQ Private Sector</t>
+  </si>
+  <si>
+    <t>1.17.4</t>
+  </si>
+  <si>
+    <t>LANAT-4: Raised bogs regeneration</t>
+  </si>
+  <si>
+    <t>1.17.7</t>
+  </si>
+  <si>
+    <t>AGR-1: Nature Park stations</t>
+  </si>
+  <si>
+    <t>1.18.4</t>
+  </si>
+  <si>
+    <t>AUE-2: Biomass Potential</t>
+  </si>
+  <si>
+    <t>1.17.8</t>
+  </si>
+  <si>
+    <t>AWN-1: Forest Fire Management</t>
+  </si>
+  <si>
+    <t>1.19.3</t>
+  </si>
+  <si>
+    <t>LANAT-1: Dienstleistung des Bodens erfassen und in Wert setzen</t>
+  </si>
+  <si>
+    <t>1.19.2</t>
+  </si>
+  <si>
+    <t>LANAT-2: Development of the Grosses Moos region</t>
+  </si>
+  <si>
+    <t>1.17.3</t>
+  </si>
+  <si>
+    <t>LANAT-3: Water body management</t>
+  </si>
+  <si>
+    <t>1.18.2</t>
+  </si>
+  <si>
+    <t>AUE-1: Climate Neutral Region Oberland-Ost</t>
+  </si>
+  <si>
+    <t>1.18.5</t>
+  </si>
+  <si>
+    <t>AWN-2: Regional Value Chains Forest and Wood</t>
+  </si>
+  <si>
+    <t>1.18.3</t>
+  </si>
+  <si>
+    <t>AUE-3: Plus-Energy City</t>
+  </si>
+  <si>
+    <t>1.18.7</t>
+  </si>
+  <si>
+    <t>AWA-1: Wyss Academy-1 Substitute Raw Materials in the Circular Economy</t>
+  </si>
+  <si>
+    <t>SP1 1.2.1</t>
+  </si>
+  <si>
+    <t>How-to Guide: Solutionscape co-design, visioning and system understanding</t>
+  </si>
+  <si>
+    <t>SP1 2.1.1</t>
+  </si>
+  <si>
+    <t>Interdisciplinary research: Artisanal mining</t>
+  </si>
+  <si>
+    <t>SP1 2.1.2</t>
+  </si>
+  <si>
+    <t>Interdisciplinary research: Agroecology</t>
+  </si>
+  <si>
+    <t>SP1 2.1.4</t>
+  </si>
+  <si>
+    <t>Interdisciplinary research: Indigenous governance</t>
+  </si>
+  <si>
+    <t>SP1 2.1.12</t>
+  </si>
+  <si>
+    <t>Interdisciplinary research: Water scarcity</t>
+  </si>
+  <si>
+    <t>SP1 2.1.11</t>
+  </si>
+  <si>
+    <t>ID Payments for ecosystem services (PES): carbon and biodiversity credits</t>
+  </si>
+  <si>
+    <t>SP1 2.1.14</t>
+  </si>
+  <si>
+    <t>Stakeholder Network Analysis (SNA) for System Transformation</t>
+  </si>
+  <si>
+    <t>EAF1 Co-design solutionscape, knowledge and engagement, monitoring</t>
+  </si>
+  <si>
+    <t>Habitat Connectivity</t>
+  </si>
+  <si>
+    <t>Rangeland quality</t>
+  </si>
+  <si>
+    <t>Alternative Livelihoods for households with limited access to Land</t>
+  </si>
+  <si>
+    <t>EAF3 Co-design solutionscape, knowledge and engagement, monitoring</t>
+  </si>
+  <si>
+    <t>1.2.1</t>
+  </si>
+  <si>
+    <t>EAF2 Co-design solutionscape, knowledge and engagement, monitoring</t>
+  </si>
+  <si>
+    <t>1.2.2</t>
+  </si>
+  <si>
+    <t>Integrated wetland management for increased biomass production and water retention</t>
+  </si>
+  <si>
+    <t>Ecosystem connectivity for improved wildlife movements and reduced HW conflicts</t>
+  </si>
+  <si>
+    <t>SAM Co-Design solutionscape, knowledge and engagement, monitoring</t>
+  </si>
+  <si>
+    <t>1.4.2</t>
+  </si>
+  <si>
+    <t>Inclusive Territorial Governance and Policy Implementation</t>
+  </si>
+  <si>
+    <t>Scaling Transformative Innovation for Resilient Livelihoods</t>
+  </si>
+  <si>
+    <t>Forest Conservation through Nature-Based Livelihoods</t>
+  </si>
+  <si>
+    <t>Productive Restoration of Degraded Landscapes</t>
+  </si>
+  <si>
+    <t>SEA Co-design solutionscape, knowledge and engagement, monitoring</t>
+  </si>
+  <si>
+    <t>1.7.1</t>
+  </si>
+  <si>
+    <t>OE Co-design, Solutionscape,knowledge and engagement, monitoring</t>
+  </si>
+  <si>
+    <t>Diversity in the Grosses Moos Region</t>
+  </si>
+  <si>
+    <t>Engaging with Other Effective Area-Based Conservation Measures (OECMs)</t>
+  </si>
+  <si>
+    <t>Adaptive culture and organisation</t>
+  </si>
+  <si>
+    <t>Monitoring, Evaluation, and Learning</t>
+  </si>
+  <si>
+    <t>3.3.3</t>
+  </si>
+  <si>
+    <t>Research (R&amp;I)</t>
+  </si>
+  <si>
+    <t>1.6.3</t>
+  </si>
+  <si>
+    <t>Umsetzungsprogramm Kanton Bern</t>
+  </si>
+  <si>
+    <t>1.5.5</t>
+  </si>
+  <si>
+    <t>Lao project phase-out</t>
+  </si>
+  <si>
+    <t>GM Co-design solutionscape, knowledge, engagement,monitoring</t>
+  </si>
+  <si>
+    <t>3.3.3.3</t>
+  </si>
+  <si>
+    <t>Research and Innovation teams: Land Systems</t>
+  </si>
+  <si>
+    <t>1.19.3.1</t>
+  </si>
+  <si>
+    <t>GS-2: Programmkoordinationsstelle des Kantons</t>
+  </si>
+  <si>
+    <t>3.3.3.3.2</t>
+  </si>
+  <si>
+    <t>Strategic Contributions to CDE Executive Management</t>
+  </si>
+  <si>
+    <t>3.3.3.3.1</t>
+  </si>
+  <si>
+    <t>Biodiversa BridgingValues</t>
+  </si>
+  <si>
+    <t>3.3.3.3.4</t>
+  </si>
+  <si>
+    <t>Climate Resilient Cocoa Landscapes Madagascar</t>
+  </si>
+  <si>
+    <t>3.3.3.3.3</t>
+  </si>
+  <si>
+    <t>Climate-resilient farming systems - SNF</t>
+  </si>
+  <si>
+    <t>3.3.3.1</t>
+  </si>
+  <si>
+    <t>Research and Innovation teams: Climate</t>
+  </si>
+  <si>
+    <t>3.3.3.2</t>
+  </si>
+  <si>
+    <t>Research and Innovation teams: Integrative Biodiversity Conservation Science</t>
+  </si>
+  <si>
+    <t>3.3.3.4</t>
+  </si>
+  <si>
+    <t>Research and Innovation teams: Environmental Governance</t>
+  </si>
+  <si>
+    <t>3.3.3.5</t>
+  </si>
+  <si>
+    <t>Research and Innovation teams: Political Economy</t>
+  </si>
+  <si>
+    <t>3.3.3.6</t>
+  </si>
+  <si>
+    <t>Peter Messerli - Teaching</t>
+  </si>
+  <si>
+    <t>1.4.4.1</t>
+  </si>
+  <si>
+    <t>Castañal Climate Innovation Pilot</t>
+  </si>
+  <si>
+    <t>2.2.2.1</t>
+  </si>
+  <si>
+    <t>Quantifying Disturbance Carbon Losses from SCB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,6 +821,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="33">
@@ -744,8 +1168,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -805,9 +1232,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -845,7 +1272,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -951,7 +1378,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1093,7 +1520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1101,10 +1528,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70066261-A730-4BDF-B964-DBA0D6823F19}">
-  <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:N108"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1112,309 +1539,1075 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B55" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B56" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B58" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="B66" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B67" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="B68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B69" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="B71" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B72" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="B73" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B74" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="B75" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" t="s">
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="B76" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" t="s">
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="B77" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B18" t="s">
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
+      <c r="B95" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
